--- a/data/fiches.xlsx
+++ b/data/fiches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,30 +461,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>auteur</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>champ_ordre</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>highlight</t>
+          <t>champ_label</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>champ_ordre</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>champ_label</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>champ_valeur</t>
         </is>
@@ -523,28 +513,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aide partielle pour la toilette</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>Autonomie</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Aide partielle pour la toilette, marche avec déambulateur</t>
         </is>
@@ -583,28 +563,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aide partielle pour la toilette</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>Régime alimentaire</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Sans sel strict</t>
         </is>
@@ -643,28 +613,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aide partielle pour la toilette</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>Allergies connues</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -703,28 +663,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aide partielle pour la toilette</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>Personne à prévenir</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Fille — Mme Dubreuil, 06 12 34 56 78</t>
         </is>
@@ -763,28 +713,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aide partielle pour la toilette</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>Dispositifs en place</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Voie veineuse périphérique ; sonde vésicale retirée le 12/05</t>
         </is>
@@ -823,24 +763,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Structure d'aval</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Hospitalisation à domicile (HAD)</t>
         </is>
@@ -879,24 +813,18 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Surveillance prévue</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Poids quotidien, diurèse, ionogramme à J3</t>
         </is>
@@ -935,24 +863,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
           <t>UF Cardiologie</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Traitement de sortie</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Furosémide 40mg 2x/j, Ramipril 5mg 1x/j</t>
         </is>
@@ -991,28 +913,18 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IDE Blanchard</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>UF Pneumologie</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>expectorations en diminution</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>Fréquence respiratoire</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>18/min, régulière</t>
         </is>
@@ -1051,28 +963,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IDE Blanchard</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
           <t>UF Pneumologie</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>expectorations en diminution</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>Oxygénothérapie</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Sevrage réalisé le 13/04</t>
         </is>
@@ -1111,28 +1013,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IDE Blanchard</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
           <t>UF Pneumologie</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>expectorations en diminution</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
           <t>Toux</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Productive, expectorations en diminution</t>
         </is>
@@ -1171,24 +1063,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kinésithérapeute Ferry</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>UF Rééducation</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
+      <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Appui</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Partiel, avec cannes anglaises</t>
         </is>
@@ -1227,24 +1113,18 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kinésithérapeute Ferry</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
           <t>UF Rééducation</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Amplitude articulaire hanche</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Flexion 70°, pas de limitation en rotation</t>
         </is>
@@ -1283,24 +1163,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kinésithérapeute Ferry</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>UF Rééducation</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Douleur (EVA)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>3/10 au repos, 5/10 à la mobilisation</t>
         </is>

--- a/data/fiches.xlsx
+++ b/data/fiches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1033,37 +1033,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REC-2024-00234</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
+          <t>REC-2024-00099</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>hf1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fiche de suivi rééducation</t>
+          <t>Fiche de coordination ville-hôpital</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rééducation</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UF Rééducation</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1071,49 +1067,45 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Appui</t>
+          <t>Médecin traitant</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Partiel, avec cannes anglaises</t>
+          <t>Dr Martin, cabinet de Belleville</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REC-2024-00234</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
+          <t>REC-2024-00099</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>hf1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fiche de suivi rééducation</t>
+          <t>Fiche de coordination ville-hôpital</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rééducation</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UF Rééducation</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1121,12 +1113,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Amplitude articulaire hanche</t>
+          <t>Pathologie de fond</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Flexion 70°, pas de limitation en rotation</t>
+          <t>BPCO stade II</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1130,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1167,14 +1159,114 @@
         </is>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Appui</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Partiel, avec cannes anglaises</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ID0000156</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fiche de suivi rééducation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rééducation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UF Rééducation</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Amplitude articulaire hanche</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Flexion 70°, pas de limitation en rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ID0000156</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fiche de suivi rééducation</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rééducation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UF Rééducation</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Douleur (EVA)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>3/10 au repos, 5/10 à la mobilisation</t>
         </is>
